--- a/artfynd/A 5721-2026 artfynd.xlsx
+++ b/artfynd/A 5721-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74464270</v>
+        <v>74574245</v>
       </c>
       <c r="B2" t="n">
-        <v>104150</v>
+        <v>109865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224416</v>
+        <v>220228</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -736,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>1984-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1992-12-31</t>
+          <t>1990-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F2d 2904. SOM: Helianthemum nummularium ssp. nummularium. LEG: Olof Svensson, Göran Wendt</t>
+          <t>Smålands flora 2007: KOO: 5F2d 2904. SOM: Leontodon hispidus. LEG: Curt Mossberg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Torr slänt</t>
+          <t>Vägkant-hasseldunge</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74574245</v>
+        <v>74464270</v>
       </c>
       <c r="B3" t="n">
-        <v>109316</v>
+        <v>104640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,23 +797,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220228</v>
+        <v>224416</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,17 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
+          <t>1992-12-31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5F2d 2904. SOM: Leontodon hispidus. LEG: Curt Mossberg</t>
+          <t>Smålands flora 2007: KOO: 5F2d 2904. SOM: Helianthemum nummularium ssp. nummularium. LEG: Olof Svensson, Göran Wendt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,7 +871,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägkant-hasseldunge</t>
+          <t>Torr slänt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
